--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.73743878273257</v>
+        <v>8.082333802194043</v>
       </c>
       <c r="D2" t="n">
-        <v>49.34985311953849</v>
+        <v>8.019351131925006</v>
       </c>
       <c r="E2" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F2" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.37581360847719</v>
+        <v>6.236069711377543</v>
       </c>
       <c r="D3" t="n">
-        <v>37.98323210321345</v>
+        <v>6.172275216772185</v>
       </c>
       <c r="E3" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F3" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.94192921359284</v>
+        <v>8.765563497208838</v>
       </c>
       <c r="D4" t="n">
-        <v>53.28909069339613</v>
+        <v>8.659477237676871</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F4" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.41634026315624</v>
+        <v>3.15515529276289</v>
       </c>
       <c r="D5" t="n">
-        <v>19.48613808220382</v>
+        <v>3.16649743835812</v>
       </c>
       <c r="E5" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F5" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.32554884496709</v>
+        <v>7.527901687307152</v>
       </c>
       <c r="D6" t="n">
-        <v>46.59012844062414</v>
+        <v>7.570895871601423</v>
       </c>
       <c r="E6" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F6" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.02066443300918</v>
+        <v>3.090857970363992</v>
       </c>
       <c r="D7" t="n">
-        <v>18.69916746133328</v>
+        <v>3.038614712466658</v>
       </c>
       <c r="E7" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F7" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.49184206312931</v>
+        <v>3.492424335258513</v>
       </c>
       <c r="D8" t="n">
-        <v>20.86294618602518</v>
+        <v>3.390228755229091</v>
       </c>
       <c r="E8" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F8" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.32673488296034</v>
+        <v>4.440594418481055</v>
       </c>
       <c r="D9" t="n">
-        <v>28.00992955740812</v>
+        <v>4.551613553078821</v>
       </c>
       <c r="E9" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F9" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.31003329563957</v>
+        <v>6.06288041054143</v>
       </c>
       <c r="D10" t="n">
-        <v>56.12035127438614</v>
+        <v>9.119557082087749</v>
       </c>
       <c r="E10" t="n">
-        <v>12.73690851094677</v>
+        <v>2.069747633028851</v>
       </c>
       <c r="F10" t="n">
-        <v>14.37012246913235</v>
+        <v>2.335144901234008</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
